--- a/branches/restrict-interpretation-vs/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/restrict-interpretation-vs/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:24:05+00:00</t>
+    <t>2026-09-01T07:36:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/restrict-interpretation-vs/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/restrict-interpretation-vs/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T07:36:06+00:00</t>
+    <t>2026-09-01T07:48:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/restrict-interpretation-vs/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/restrict-interpretation-vs/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T07:48:18+00:00</t>
+    <t>2026-09-01T07:55:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/restrict-interpretation-vs/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/restrict-interpretation-vs/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T07:55:52+00:00</t>
+    <t>2026-09-01T08:05:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/restrict-interpretation-vs/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/restrict-interpretation-vs/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:05:25+00:00</t>
+    <t>2026-09-01T08:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
